--- a/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -777,10 +777,105 @@
       <c r="A41" t="str">
         <v>7</v>
       </c>
+      <c r="C41" t="str">
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>514_松虫草紫_scabiosa purple_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="C43" t="str" xml:space="preserve">
+        <v xml:space="preserve">511_黑种草白色_nigella damascena 
+white_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>563_星芹_Astrantia_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>563_星芹_Astrantia_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>770_弯葱_undefined_undefined_10stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>8</v>
+      </c>
+      <c r="C48" t="str">
+        <v>504_大花葱_Allium _undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
+        <v>9</v>
+      </c>
+      <c r="C49" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
+        <v>10</v>
+      </c>
+      <c r="C50" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -835,7 +930,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0128551015551065515555530302051510555.527100100100851015151010550</v>
+        <v>0128551015551065515555530302051510555.5271001001008510151510105510101055101015550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
@@ -870,7 +870,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
@@ -870,7 +870,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -870,12 +870,458 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
+        <v>11</v>
+      </c>
+      <c r="C51" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>12</v>
+      </c>
+      <c r="C55" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
         <v>1</v>
+      </c>
+      <c r="C58" t="str">
+        <v>849_婚庆卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>849_婚庆卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>843_灯台_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>571_大飞燕浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2</v>
+      </c>
+      <c r="C63" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F63" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F64" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>111_绣球紫粉_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F66" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F67" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F68" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>1</v>
+      </c>
+      <c r="C69" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F69" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F70" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F71" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F72" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F73" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2</v>
+      </c>
+      <c r="C74" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F74" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F75" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F76" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F77" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F78" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F79" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>3</v>
+      </c>
+      <c r="C80" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="str">
+        <v>757_芍药老忠诚_Old Faith_undefined_10stems</v>
+      </c>
+      <c r="F81" t="str">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" t="str">
+        <v>761_芍药奶油碗_undefined_undefined_10stems</v>
+      </c>
+      <c r="F82" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>4</v>
+      </c>
+      <c r="C83" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F83" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F84" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="str">
+        <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
+      </c>
+      <c r="F85" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F86" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F87" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F88" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F89" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" t="str">
+        <v>247_苏芬_Sofine_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F90" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F91" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="C92" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F92" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="C93" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F93" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F94" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F95" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F96" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="C97" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F97" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>5</v>
+      </c>
+      <c r="C98" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F98" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" t="str">
+        <v>822_剑兰红丝绒_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F99" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="C100" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F100" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="C101" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F101" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" t="str">
+        <v>247_苏芬_Sofine_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F102" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="C103" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F103" t="str">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -930,7 +1376,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0128551015551065515555530302051510555.5271001001008510151510105510101055101015550</v>
+        <v>0128551015551065515555530302051510555.52710010010085101515101055101010551010155511215750.5952055109852030391057585109110851105020155105555555105551155532</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-1.xlsx
@@ -1378,6 +1378,9 @@
       <c r="G2" t="str">
         <v>0128551015551065515555530302051510555.52710010010085101515101055101010551010155511215750.5952055109852030391057585109110851105020155105555555105551155532</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
